--- a/library/seed/04_Arknights_Endfield.xlsx
+++ b/library/seed/04_Arknights_Endfield.xlsx
@@ -1,720 +1,997 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Characters" sheetId="1" r:id="rId1"/>
+    <sheet name="Characters" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя персонажа</t>
+          <t>Имя персонажа</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стихия</t>
+          <t>Стихия</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Редкость</t>
+          <t>Редкость</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arcane</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Arcane</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ardelia</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Ardelia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camille</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ember</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilberta</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Gilberta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laevatain</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Laevatain</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last Rite</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Last Rite</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lifeng</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Lifeng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liino</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Liino</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.10</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mi Fu</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Mi Fu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.11</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogranichnik</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Pogranichnik</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.12</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rossi</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.13</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangtang</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Tangtang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.14</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typhoeus</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Typhoeus</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.15</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yvonne</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Yvonne</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.16</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhuang Fangyi</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Zhuang Fangyi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.17</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alesh</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Alesh</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.18</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arclight</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Arclight</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.19</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avywenna</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Avywenna</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.20</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen Qianyu</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Chen Qianyu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.21</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Da Pan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Da Pan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.22</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perlica</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Perlica</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.23</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purrchena</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Purrchena</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.24</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snowshine</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Snowshine</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.25</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wulfgard</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Wulfgard</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.26</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xaihi</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Xaihi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akekuri</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Akekuri</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.28</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antal</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Antal</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.29</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catcher</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Catcher</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estella</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Estella</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.31</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluorite</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>Fluorite</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/library/seed/04_Arknights_Endfield.xlsx
+++ b/library/seed/04_Arknights_Endfield.xlsx
@@ -444,7 +444,6 @@
           <t>Arcane</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>6★</t>
@@ -462,7 +461,6 @@
           <t>Ardelia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>6★</t>
@@ -480,7 +478,6 @@
           <t>Camille</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>6★</t>
@@ -498,7 +495,6 @@
           <t>Ember</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>6★</t>
@@ -516,7 +512,6 @@
           <t>Gilberta</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>6★</t>
@@ -534,7 +529,6 @@
           <t>Laevatain</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>6★</t>
@@ -552,7 +546,6 @@
           <t>Last Rite</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>6★</t>
@@ -570,7 +563,6 @@
           <t>Lifeng</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>6★</t>
@@ -588,7 +580,6 @@
           <t>Liino</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>6★</t>
@@ -606,7 +597,6 @@
           <t>Mi Fu</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>6★</t>
@@ -624,7 +614,6 @@
           <t>Pogranichnik</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>6★</t>
@@ -642,7 +631,6 @@
           <t>Rossi</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>6★</t>
@@ -660,7 +648,6 @@
           <t>Tangtang</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>6★</t>
@@ -678,7 +665,6 @@
           <t>Typhoeus</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>6★</t>
@@ -696,7 +682,6 @@
           <t>Yvonne</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>6★</t>
@@ -714,7 +699,6 @@
           <t>Zhuang Fangyi</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>6★</t>
@@ -732,7 +716,6 @@
           <t>Alesh</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>5★</t>
@@ -750,7 +733,6 @@
           <t>Arclight</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>5★</t>
@@ -768,7 +750,6 @@
           <t>Avywenna</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>5★</t>
@@ -786,7 +767,6 @@
           <t>Chen Qianyu</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>5★</t>
@@ -804,7 +784,6 @@
           <t>Da Pan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>5★</t>
@@ -822,7 +801,6 @@
           <t>Perlica</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>5★</t>
@@ -840,7 +818,6 @@
           <t>Purrchena</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>5★</t>
@@ -858,7 +835,6 @@
           <t>Snowshine</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>5★</t>
@@ -876,7 +852,6 @@
           <t>Wulfgard</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>5★</t>
@@ -894,7 +869,6 @@
           <t>Xaihi</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>5★</t>
@@ -912,7 +886,6 @@
           <t>Akekuri</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>4★</t>
@@ -930,7 +903,6 @@
           <t>Antal</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>4★</t>
@@ -948,7 +920,6 @@
           <t>Catcher</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>4★</t>
@@ -966,7 +937,6 @@
           <t>Estella</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>4★</t>
@@ -984,7 +954,6 @@
           <t>Fluorite</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>4★</t>

--- a/library/seed/04_Arknights_Endfield.xlsx
+++ b/library/seed/04_Arknights_Endfield.xlsx
@@ -1,614 +1,992 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos"/>
       <sz val="11"/>
-      <name val="Aptos"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя персонажа</t>
+          <t>Имя персонажа</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стихия</t>
+          <t>Стихия</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Редкость</t>
+          <t>Редкость</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arcane</t>
+          <t>Arcane</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ardelia</t>
+          <t>Ardelia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camille</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ember</t>
+          <t>Ember</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilberta</t>
+          <t>Gilberta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laevatain</t>
+          <t>Laevatain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last Rite</t>
+          <t>Last Rite</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lifeng</t>
+          <t>Lifeng</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liino</t>
+          <t>Liino</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.10</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mi Fu</t>
+          <t>Mi Fu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.11</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogranichnik</t>
+          <t>Pogranichnik</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.12</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rossi</t>
+          <t>Rossi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.13</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangtang</t>
+          <t>Tangtang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.14</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typhoeus</t>
+          <t>Typhoeus</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.15</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yvonne</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.16</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhuang Fangyi</t>
+          <t>Zhuang Fangyi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6★</t>
+          <t>6★</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.17</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alesh</t>
+          <t>Alesh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.18</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arclight</t>
+          <t>Arclight</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.19</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avywenna</t>
+          <t>Avywenna</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.20</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen Qianyu</t>
+          <t>Chen Qianyu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.21</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Da Pan</t>
+          <t>Da Pan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.22</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perlica</t>
+          <t>Perlica</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.23</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purrchena</t>
+          <t>Purrchena</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.24</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snowshine</t>
+          <t>Snowshine</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.25</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wulfgard</t>
+          <t>Wulfgard</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.26</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xaihi</t>
+          <t>Xaihi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akekuri</t>
+          <t>Akekuri</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.28</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antal</t>
+          <t>Antal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.29</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catcher</t>
+          <t>Catcher</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estella</t>
+          <t>Estella</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.31</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluorite</t>
+          <t>Fluorite</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4★</t>
+          <t>4★</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.32</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cryo</t>
+          <t>Cryo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5★</t>
+          <t>5★</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>